--- a/output/resisto/sample_resisto/TC00856554_S51.xlsx
+++ b/output/resisto/sample_resisto/TC00856554_S51.xlsx
@@ -425,33 +425,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Drug</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Gene</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Coding region change</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Amino acid change</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Level</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Frequency // Coverage // Zero coverage bases // Mapped reads</t>
         </is>
       </c>
     </row>
@@ -461,27 +471,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Ethionamide</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>inhA</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>inhA_c.-777C&gt;T</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>inhA_c.-777C&gt;T</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>1) Assoc w R</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>100.0 // 170 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -491,27 +511,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Isoniazid</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>inhA</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>inhA_c.-777C&gt;T</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>inhA_c.-777C&gt;T</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>1) Assoc w R</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>100.0 // 170 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -521,27 +551,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Levofloxacin</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>gyrA</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>NP_214520.1:c.61G&gt;C</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>NP_214520.1:p.Glu21Gln</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>100.0 // 134 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -551,27 +591,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Moxifloxacin</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>gyrA</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>NP_214520.1:c.61G&gt;C</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>NP_214520.1:p.Glu21Gln</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>100.0 // 134 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -581,27 +631,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Levofloxacin</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>gyrA</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>NP_214520.1:c.284G&gt;C</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>NP_214520.1:p.Ser95Thr</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>99.173553719 // 121 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -611,27 +671,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Moxifloxacin</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>gyrA</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>NP_214520.1:c.284G&gt;C</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>NP_214520.1:p.Ser95Thr</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>99.173553719 // 121 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -641,27 +711,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Levofloxacin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>gyrA</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>NP_214520.1:c.2003G&gt;A</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>NP_214520.1:p.Gly668Asp</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>99.3902439024 // 164 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -671,27 +751,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Moxifloxacin</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>gyrA</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>NP_214520.1:c.2003G&gt;A</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>NP_214520.1:p.Gly668Asp</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>99.3902439024 // 164 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -701,27 +791,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Clofazimine</t>
+          <t>TC00856554_S51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Delamanid</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>fgd1</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>NP_214921.1:c.960T&gt;C</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>98.6486486486 // 148 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -731,27 +831,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Delamanid</t>
+          <t>TC00856554_S51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Clofazimine</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>fgd1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>NP_214921.1:c.960T&gt;C</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>98.6486486486 // 148 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -761,27 +871,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Isoniazid</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>mshA</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>NP_215000.1:c.560C&gt;T</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>NP_215000.1:p.Ala187Val</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>100.0 // 154 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -791,27 +911,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>Ethionamide</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>mshA</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>NP_215000.1:c.560C&gt;T</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>NP_215000.1:p.Ala187Val</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>100.0 // 154 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -821,27 +951,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Kanamycin</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>ccsA</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>NP_215041.2:c.735A&gt;G</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>NP_215041.2:p.Ile245Met</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>99.3788819876 // 161 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -851,27 +991,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Capreomycin</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>ccsA</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>NP_215041.2:c.735A&gt;G</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>NP_215041.2:p.Ile245Met</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>99.3788819876 // 161 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -881,27 +1031,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Amikacin</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>ccsA</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>NP_215041.2:c.735A&gt;G</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>NP_215041.2:p.Ile245Met</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>99.3788819876 // 161 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -911,27 +1071,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Ethionamide</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Rv0565c</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>NP_215079.1:c.390G&gt;A</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>100.0 // 168 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -941,27 +1111,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Ethionamide</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Rv0565c</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>NP_215079.1:c.329G&gt;A</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>NP_215079.1:p.Arg110His</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>100.0 // 170 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -971,27 +1151,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Rifampicin</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>rpoB</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>NP_215181.1:c.1349C&gt;T</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>NP_215181.1:p.Ser450Leu</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>100.0 // 151 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1001,27 +1191,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Rifamycin</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>rpoB</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>NP_215181.1:c.1349C&gt;T</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>NP_215181.1:p.Ser450Leu</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>100.0 // 151 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1031,27 +1231,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Rifampicin</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>rpoB</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>NP_215181.1:c.3225T&gt;C</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>98.0132450331 // 151 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1061,27 +1271,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Rifamycin</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>rpoB</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>NP_215181.1:c.3225T&gt;C</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>98.0132450331 // 151 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1091,27 +1311,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Rifampicin</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>rpoC</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>NP_215182.1:c.186C&gt;T</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>99.4505494505 // 182 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1121,27 +1351,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Rifampicin</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>rpoC</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>NP_215182.1:c.3330G&gt;T</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>NP_215182.1:p.Gln1110His</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>100.0 // 151 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1151,27 +1391,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Clofazimine</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>mmpL5</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>NP_215190.1:c.2842A&gt;G</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>NP_215190.1:p.Ile948Val</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>96.5517241379 // 145 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1431,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>Bedaquiline</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>mmpL5</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>NP_215190.1:c.2842A&gt;G</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>NP_215190.1:p.Ile948Val</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>96.5517241379 // 145 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1211,27 +1471,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Clofazimine</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>mmpL5</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>NP_215190.1:c.2381C&gt;T</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>NP_215190.1:p.Thr794Ile</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>99.3670886076 // 158 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1241,27 +1511,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>Bedaquiline</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>mmpL5</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>NP_215190.1:c.2381C&gt;T</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>NP_215190.1:p.Thr794Ile</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>99.3670886076 // 158 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1271,27 +1551,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>Clofazimine</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>mmpL5</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>NP_215190.1:c.2299G&gt;A</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>NP_215190.1:p.Asp767Asn</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>100.0 // 142 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1301,27 +1591,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>Bedaquiline</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>mmpL5</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>NP_215190.1:c.2299G&gt;A</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>NP_215190.1:p.Asp767Asn</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>100.0 // 142 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1331,27 +1631,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Isoniazid</t>
+          <t>TC00856554_S51</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>Pyrazinamide</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>Rv1258c</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>NP_215774.1:c.580_581insC</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>NP_215774.1:p.Glu194fs</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>98.5401459854 // 137 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1361,27 +1671,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>Streptomycin</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Rv1258c</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>NP_215774.1:c.580_581insC</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>NP_215774.1:p.Glu194fs</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>98.5401459854 // 137 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1391,27 +1711,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pyrazinamide</t>
+          <t>TC00856554_S51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Isoniazid</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>Rv1258c</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>NP_215774.1:c.580_581insC</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>NP_215774.1:p.Glu194fs</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>98.5401459854 // 137 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1421,27 +1751,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>Isoniazid</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>inhA</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>inhA promoter:c.15G&gt;A</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>100.0 // 170 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1451,27 +1791,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>Ethionamide</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>inhA</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>inhA promoter:c.15G&gt;A</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>100.0 // 170 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1481,27 +1831,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>Pyrazinamide</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>rpsA</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>NP_216146.1:c.636A&gt;C</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>100.0 // 159 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1511,27 +1871,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>Linezolid</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>tsnR</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>NP_216160.1:c.695T&gt;C</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>NP_216160.1:p.Leu232Pro</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>100.0 // 146 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1541,27 +1911,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>Capreomycin</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>tlyA</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>NP_216210.1:c.33A&gt;G</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>99.375 // 160 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1571,27 +1951,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>Aminoglycoside</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>tlyA</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>NP_216210.1:c.33A&gt;G</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>99.375 // 160 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1601,27 +1991,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>Isoniazid</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>katG</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>NP_216424.1:c.1388G&gt;T</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>NP_216424.1:p.Arg463Leu</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>100.0 // 160 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1631,27 +2031,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>Pyrazinamide</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>PPE35</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>YP_177850.1:c.2687T&gt;C</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>YP_177850.1:p.Leu896Ser</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>100.0 // 155 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1661,27 +2071,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>Pyrazinamide</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Rv3236c</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>YP_177949.1:c.304A&gt;G</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>YP_177949.1:p.Thr102Ala</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>100.0 // 153 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1691,27 +2111,37 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>Rifampicin</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>mtrB</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>NP_217762.1:c.1549A&gt;C</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>NP_217762.1:p.Met517Leu</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>100.0 // 132 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1721,27 +2151,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>Bedaquiline</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>mtrB</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>NP_217762.1:c.1549A&gt;C</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>NP_217762.1:p.Met517Leu</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>100.0 // 132 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1751,27 +2191,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>Rifampicin</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>mtrB</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>NP_217762.1:c.52C&gt;T</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>NP_217762.1:p.Pro18Ser</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>100.0 // 178 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1781,27 +2231,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>Bedaquiline</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>mtrB</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>NP_217762.1:c.52C&gt;T</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>NP_217762.1:p.Pro18Ser</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>100.0 // 178 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1811,27 +2271,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>Ethamobutol</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>manB</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>YP_177951.1:c.534C&gt;A</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>97.1264367816 // 174 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1841,27 +2311,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>Ethambutol</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>embC</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>NP_218310.1:c.2781C&gt;T</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>100.0 // 166 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1871,27 +2351,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>Ethambutol</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>embA</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>NP_218311.1:c.228C&gt;T</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>100.0 // 170 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1901,27 +2391,37 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>Ethambutol</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>embB</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>NP_218312.1:c.916A&gt;G</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>NP_218312.1:p.Met306Val</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>100.0 // 146 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1931,27 +2431,37 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>Ethambutol</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>aftB</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>NP_218322.1:c.1190A&gt;G</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>NP_218322.1:p.Asp397Gly</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>100.0 // 149 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1961,27 +2471,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>Ethionamide</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>ethR</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>NP_218372.1:c.283G&gt;A</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>NP_218372.1:p.Ala95Thr</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>100.0 // 145 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -1991,27 +2511,37 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>Streptomycin</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>gid</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>NP_218436.2:c.615A&gt;G</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>99.4117647059 // 170 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2021,27 +2551,37 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>Streptomycin</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>gid</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>NP_218436.2:c.276A&gt;C</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>NP_218436.2:p.Glu92Asp</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Ungraded</t>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ungraded</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>100.0 // 119 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2051,27 +2591,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>Rifamycin</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>rpoB</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>rpoB_1349C&gt;T</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>rpoB_Ser450Leu</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>100.0 // 151 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2081,27 +2631,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>Isoniazid</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>katG</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>katG_1388G&gt;T</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>katG_Arg463Leu</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>S</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>100.0 // 160 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2111,27 +2671,37 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>Ethambutol</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>embB</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>embB_916A&gt;G</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>embB_Met306Val</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>100.0 // 146 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2141,27 +2711,37 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>Ethionamide</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>ethR</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>ethR_283G&gt;A</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>ethR_Ala95Thr</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>100.0 // 145 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2171,27 +2751,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>Streptomycin</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>gid</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>gid_276A&gt;C</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>gid_Glu92Asp</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>100.0 // 119 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2201,27 +2791,37 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>Levofloxacin</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>gyrA</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>gyrA_c.61G&gt;C</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>gyrA_p.Glu21Gln</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>100.0 // 134 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2231,27 +2831,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>Moxifloxacin</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>gyrA</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>gyrA_c.61G&gt;C</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>gyrA_p.Glu21Gln</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>100.0 // 134 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2261,27 +2871,37 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>Levofloxacin</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>gyrA</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>gyrA_c.284G&gt;C</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>gyrA_p.Ser95Thr</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>99.173553719 // 121 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2291,27 +2911,37 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>Moxifloxacin</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>gyrA</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>gyrA_c.284G&gt;C</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>gyrA_p.Ser95Thr</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>99.173553719 // 121 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2321,27 +2951,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>Levofloxacin</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>gyrA</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>gyrA_c.2003G&gt;A</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>gyrA_p.Gly668Asp</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>99.3902439024 // 164 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2351,27 +2991,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
           <t>Moxifloxacin</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>gyrA</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>gyrA_c.2003G&gt;A</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>gyrA_p.Gly668Asp</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>99.3902439024 // 164 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2381,27 +3031,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>Clofazimine</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>fgd1</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>fgd1_c.960T&gt;C</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>98.6486486486 // 148 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2411,27 +3071,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>Delamanid</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>fgd1</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>fgd1_c.960T&gt;C</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>4) Not assoc w R - Interim</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>98.6486486486 // 148 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2441,27 +3111,37 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
           <t>Ethionamide</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>mshA</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>mshA_c.560C&gt;T</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>mshA_p.Ala187Val</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>100.0 // 154 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2471,27 +3151,37 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
           <t>Isoniazid</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>mshA</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>mshA_c.560C&gt;T</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>mshA_p.Ala187Val</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>100.0 // 154 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2501,27 +3191,37 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
           <t>Amikacin</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>ccsA</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>ccsA_c.735A&gt;G</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>ccsA_p.Ile245Met</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>99.3788819876 // 161 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2531,27 +3231,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
           <t>Capreomycin</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>ccsA</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>ccsA_c.735A&gt;G</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>ccsA_p.Ile245Met</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>99.3788819876 // 161 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2561,27 +3271,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
           <t>Kanamycin</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>ccsA</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>ccsA_c.735A&gt;G</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>ccsA_p.Ile245Met</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>3) Uncertain significance</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>99.3788819876 // 161 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2591,27 +3311,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>Ethionamide</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>Rv0565c</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Rv0565c_c.390G&gt;A</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>4) Not assoc w R - Interim</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>100.0 // 168 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2621,27 +3351,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
           <t>Ethionamide</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>Rv0565c</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>Rv0565c_c.329G&gt;A</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Rv0565c_p.Arg110His</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>3) Uncertain significance</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>100.0 // 170 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2651,27 +3391,37 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
           <t>Rifampicin</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>rpoB</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>rpoB_c.1349C&gt;T</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>rpoB_p.Ser450Leu</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>1) Assoc w R</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>100.0 // 151 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2681,27 +3431,37 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
           <t>Rifampicin</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>rpoB</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>rpoB_c.3225T&gt;C</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>98.0132450331 // 151 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2711,27 +3471,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
           <t>Rifampicin</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>rpoC</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>rpoC_c.186C&gt;T</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>4) Not assoc w R - Interim</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>99.4505494505 // 182 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2741,27 +3511,37 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
           <t>Rifampicin</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>rpoC</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>rpoC_c.3330G&gt;T</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>rpoC_p.Gln1110His</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>3) Uncertain significance</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>100.0 // 151 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2771,27 +3551,37 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
           <t>Bedaquiline</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>mmpL5</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>mmpL5_c.2842A&gt;G</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>mmpL5_p.Ile948Val</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>4) Not assoc w R - Interim</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>96.5517241379 // 145 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2801,27 +3591,37 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
           <t>Clofazimine</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>mmpL5</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>mmpL5_c.2842A&gt;G</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>mmpL5_p.Ile948Val</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>96.5517241379 // 145 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2831,27 +3631,37 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
           <t>Bedaquiline</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>mmpL5</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>mmpL5_c.2381C&gt;T</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>mmpL5_p.Thr794Ile</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>4) Not assoc w R - Interim</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>99.3670886076 // 158 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2861,27 +3671,37 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
           <t>Clofazimine</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>mmpL5</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>mmpL5_c.2381C&gt;T</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>mmpL5_p.Thr794Ile</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>99.3670886076 // 158 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2891,27 +3711,37 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
           <t>Bedaquiline</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>mmpL5</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>mmpL5_c.2299G&gt;A</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>mmpL5_p.Asp767Asn</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>100.0 // 142 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2921,27 +3751,37 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
           <t>Clofazimine</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>mmpL5</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>mmpL5_c.2299G&gt;A</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>mmpL5_p.Asp767Asn</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>100.0 // 142 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2951,27 +3791,37 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
           <t>Isoniazid</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>Rv1258c</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>Rv1258c_c.580_581insC</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Rv1258c_p.Glu194fs</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>98.5401459854 // 137 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -2981,27 +3831,37 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
           <t>Pyrazinamide</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>Rv1258c</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Rv1258c_c.580_581insC</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Rv1258c_p.Glu194fs</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>3) Uncertain significance</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>98.5401459854 // 137 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3011,27 +3871,37 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
           <t>Streptomycin</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Rv1258c</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Rv1258c_c.580_581insC</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Rv1258c_p.Glu194fs</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>98.5401459854 // 137 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3041,27 +3911,37 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>Pyrazinamide</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>rpsA</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>rpsA_c.636A&gt;C</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>4) Not assoc w R - Interim</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>100.0 // 159 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3071,27 +3951,37 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
           <t>Linezolid</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>tsnR</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>tsnR_c.695T&gt;C</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>tsnR_p.Leu232Pro</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>100.0 // 146 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3101,27 +3991,37 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
           <t>Capreomycin</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>tlyA</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>tlyA_c.33A&gt;G</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>99.375 // 160 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3131,27 +4031,37 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
           <t>Isoniazid</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>katG</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>katG_c.1388G&gt;T</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>katG_p.Arg463Leu</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>100.0 // 160 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3161,27 +4071,37 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
           <t>Pyrazinamide</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>PPE35</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>PPE35_c.2687T&gt;C</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>PPE35_p.Leu896Ser</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>100.0 // 155 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3191,27 +4111,37 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
           <t>Pyrazinamide</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Rv3236c</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>Rv3236c_c.304A&gt;G</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Rv3236c_p.Thr102Ala</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>4) Not assoc w R - Interim</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>100.0 // 153 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3221,27 +4151,37 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
           <t>Bedaquiline</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>mtrB</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>mtrB_c.1549A&gt;C</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>mtrB_p.Met517Leu</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>3) Uncertain significance</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>100.0 // 132 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3251,27 +4191,37 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
           <t>Rifampicin</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>mtrB</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>mtrB_c.1549A&gt;C</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>mtrB_p.Met517Leu</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>100.0 // 132 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3281,27 +4231,37 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
           <t>Bedaquiline</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>mtrB</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>mtrB_c.52C&gt;T</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>mtrB_p.Pro18Ser</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>3) Uncertain significance</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>100.0 // 178 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3311,27 +4271,37 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
           <t>Rifampicin</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>mtrB</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>mtrB_c.52C&gt;T</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>mtrB_p.Pro18Ser</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>100.0 // 178 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3341,27 +4311,37 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
           <t>Ethambutol</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>embC</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>embC_c.2781C&gt;T</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>100.0 // 166 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3371,27 +4351,37 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
           <t>Ethambutol</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>embA</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>embA_c.228C&gt;T</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>100.0 // 170 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3401,27 +4391,37 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
           <t>Ethambutol</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>embB</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>embB_c.916A&gt;G</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>embB_p.Met306Val</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>1) Assoc w R</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>100.0 // 146 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3431,27 +4431,37 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
           <t>Ethambutol</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>aftB</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>aftB_c.1190A&gt;G</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>aftB_p.Asp397Gly</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>100.0 // 149 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3461,27 +4471,37 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
           <t>Ethionamide</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>ethR</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>ethR_c.283G&gt;A</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>ethR_p.Ala95Thr</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>3) Uncertain significance</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>100.0 // 145 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3491,27 +4511,37 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
           <t>Streptomycin</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>gid</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>gid_c.615A&gt;G</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>99.4117647059 // 170 // 0 // 5786047</t>
         </is>
       </c>
     </row>
@@ -3521,27 +4551,37 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
+          <t>TC00856554_S51</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
           <t>Streptomycin</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>gid</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>gid_c.276A&gt;C</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>gid_p.Glu92Asp</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>5) Not assoc w R</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>100.0 // 119 // 0 // 5786047</t>
         </is>
       </c>
     </row>
